--- a/real_estate_forms/010_home_buyer_consultation_questionnaire_form--real_estate_forms.xlsx
+++ b/real_estate_forms/010_home_buyer_consultation_questionnaire_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'single_family_home'}</t>
+          <t>single_family_home</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Single Family Home'}</t>
+          <t>Single Family Home</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'townhouse'}</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Townhouse'}</t>
+          <t>Townhouse</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'condo'}</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Condo'}</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'city'}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'City'}</t>
+          <t>City</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'suburbs'}</t>
+          <t>suburbs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Suburbs'}</t>
+          <t>Suburbs</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'rural'}</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Rural'}</t>
+          <t>Rural</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'corner_lot'}</t>
+          <t>corner_lot</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Corner Lot'}</t>
+          <t>Corner Lot</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'linear_lot'}</t>
+          <t>linear_lot</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Linear Lot'}</t>
+          <t>Linear Lot</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'cul-de-sac_lot'}</t>
+          <t>cul-de-sac_lot</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Cul-de-sac Lot'}</t>
+          <t>Cul-de-sac Lot</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'ocean_view'}</t>
+          <t>ocean_view</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Ocean View'}</t>
+          <t>Ocean View</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'mountain_view'}</t>
+          <t>mountain_view</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Mountain View'}</t>
+          <t>Mountain View</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'city_view'}</t>
+          <t>city_view</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'City View'}</t>
+          <t>City View</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'country_view'}</t>
+          <t>country_view</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Country View'}</t>
+          <t>Country View</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'pool'}</t>
+          <t>pool</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Pool'}</t>
+          <t>Pool</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'gourmet_kitchen'}</t>
+          <t>gourmet_kitchen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Gourmet Kitchen'}</t>
+          <t>Gourmet Kitchen</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'high_ceilings'}</t>
+          <t>high_ceilings</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'High Ceilings'}</t>
+          <t>High Ceilings</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'large_kitchen_island'}</t>
+          <t>large_kitchen_island</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Large Kitchen Island'}</t>
+          <t>Large Kitchen Island</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'very_safe'}</t>
+          <t>very_safe</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Very Safe'}</t>
+          <t>Very Safe</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'somewhat_safe'}</t>
+          <t>somewhat_safe</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Somewhat Safe'}</t>
+          <t>Somewhat Safe</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'somewhat_not_safe'}</t>
+          <t>somewhat_not_safe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Somewhat Not Safe'}</t>
+          <t>Somewhat Not Safe</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'not_safe'}</t>
+          <t>not_safe</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Not Safe'}</t>
+          <t>Not Safe</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'very_active'}</t>
+          <t>very_active</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Very Active'}</t>
+          <t>Very Active</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'somewhat_active'}</t>
+          <t>somewhat_active</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Somewhat Active'}</t>
+          <t>Somewhat Active</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'somewhat_not_active'}</t>
+          <t>somewhat_not_active</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Somewhat Not Active'}</t>
+          <t>Somewhat Not Active</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'not_active'}</t>
+          <t>not_active</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Not Active'}</t>
+          <t>Not Active</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'very_recreational'}</t>
+          <t>very_recreational</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Very Recreational'}</t>
+          <t>Very Recreational</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'somewhat_recreational'}</t>
+          <t>somewhat_recreational</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Somewhat Recreational'}</t>
+          <t>Somewhat Recreational</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'somewhat_not_recreational'}</t>
+          <t>somewhat_not_recreational</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Somewhat Not Recreational'}</t>
+          <t>Somewhat Not Recreational</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'not_recreational'}</t>
+          <t>not_recreational</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Not Recreational'}</t>
+          <t>Not Recreational</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'very_affordable'}</t>
+          <t>very_affordable</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Very Affordable'}</t>
+          <t>Very Affordable</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'somewhat_affordable'}</t>
+          <t>somewhat_affordable</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Somewhat Affordable'}</t>
+          <t>Somewhat Affordable</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'somewhat_not_affordable'}</t>
+          <t>somewhat_not_affordable</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Somewhat Not Affordable'}</t>
+          <t>Somewhat Not Affordable</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'not_affordable'}</t>
+          <t>not_affordable</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Not Affordable'}</t>
+          <t>Not Affordable</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'single_family'}</t>
+          <t>single_family</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Single Family'}</t>
+          <t>Single Family</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'townhouse'}</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Townhouse'}</t>
+          <t>Townhouse</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'condo'}</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Condo'}</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'pool'}</t>
+          <t>pool</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Pool'}</t>
+          <t>Pool</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'gourmet_kitchen'}</t>
+          <t>gourmet_kitchen</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Gourmet Kitchen'}</t>
+          <t>Gourmet Kitchen</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'high_ceilings'}</t>
+          <t>high_ceilings</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'High Ceilings'}</t>
+          <t>High Ceilings</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'large_kitchen_island'}</t>
+          <t>large_kitchen_island</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Large Kitchen Island'}</t>
+          <t>Large Kitchen Island</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
